--- a/Interstellar Imperium/data/campaign/rules.xlsx
+++ b/Interstellar Imperium/data/campaign/rules.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26501"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Program Files (x86)\Fractal Softworks\Starsector\mods\Interstellar Imperium\data\campaign\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B342951D-02FE-477D-98C4-B3025CFC4C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225"/>
   </bookViews>
   <sheets>
     <sheet name="rules" sheetId="1" r:id="rId1"/>
@@ -1537,9 +1531,6 @@
 FireAll IIJustitiaIntroductionOptions</t>
   </si>
   <si>
-    <t>Justitia clicks her nonexitent tongue and gives you a withering look of disappointment. "That was terribly rude and hurtful, $playerName. Your mother should have washed your mouth out with soap when you were younger."</t>
-  </si>
-  <si>
     <t>$iiAskedGrandmother = true 0
 $iiAskedSomething = true 0
 $iiShowCreepy = true 0</t>
@@ -1905,11 +1896,14 @@
     <t>$option == iiTitanStrikeGoBack
 !II_NotNex score:10</t>
   </si>
+  <si>
+    <t>Justitia clicks her nonexistent tongue and gives you a withering look of disappointment. "That was terribly rude and hurtful, $playerName. Your mother should have washed your mouth out with soap when you were younger."</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2452,9 +2446,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2492,7 +2486,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2564,7 +2558,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2737,7 +2731,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G161"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3483,16 +3477,16 @@
     </row>
     <row r="52" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>525</v>
+      </c>
+      <c r="B52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>526</v>
-      </c>
-      <c r="B52" t="s">
-        <v>30</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>527</v>
       </c>
       <c r="G52"/>
     </row>
@@ -3687,19 +3681,19 @@
     </row>
     <row r="67" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>449</v>
+      </c>
+      <c r="B67" t="s">
+        <v>30</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="B67" t="s">
-        <v>30</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>451</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>308</v>
@@ -4332,7 +4326,7 @@
         <v>302</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>320</v>
@@ -4353,7 +4347,7 @@
         <v>302</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>350</v>
@@ -4661,10 +4655,10 @@
         <v>330</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4762,10 +4756,10 @@
         <v>400</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>418</v>
@@ -4779,13 +4773,13 @@
         <v>30</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>418</v>
@@ -4810,19 +4804,19 @@
     </row>
     <row r="130" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>468</v>
+      </c>
+      <c r="B130" t="s">
+        <v>30</v>
+      </c>
+      <c r="C130" s="1" t="s">
         <v>469</v>
-      </c>
-      <c r="B130" t="s">
-        <v>30</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>470</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>329</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -4839,7 +4833,7 @@
         <v>425</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>426</v>
+        <v>528</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -4853,67 +4847,67 @@
         <v>405</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>433</v>
+      </c>
+      <c r="B133" t="s">
+        <v>30</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="F133" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="B133" t="s">
-        <v>30</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>435</v>
+      </c>
+      <c r="B134" t="s">
+        <v>30</v>
+      </c>
+      <c r="C134" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="B134" t="s">
-        <v>30</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>437</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>329</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B135" t="s">
         <v>30</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>329</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -4927,27 +4921,27 @@
         <v>406</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>445</v>
+      </c>
+      <c r="B137" t="s">
+        <v>30</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B137" t="s">
-        <v>30</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>447</v>
-      </c>
       <c r="D137" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="90" x14ac:dyDescent="0.25">
@@ -4961,64 +4955,64 @@
         <v>407</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E138" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="F138" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B139" t="s">
         <v>30</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B140" t="s">
         <v>30</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D140" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="E140" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B141" t="s">
         <v>30</v>
       </c>
       <c r="C141" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="E141" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="75" x14ac:dyDescent="0.25">
@@ -5032,67 +5026,67 @@
         <v>413</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>471</v>
+      </c>
+      <c r="B143" t="s">
+        <v>30</v>
+      </c>
+      <c r="C143" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B143" t="s">
-        <v>30</v>
-      </c>
-      <c r="C143" s="1" t="s">
+      <c r="D143" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="F143" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B144" t="s">
         <v>30</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>329</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B145" t="s">
         <v>30</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>329</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -5106,186 +5100,186 @@
         <v>408</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B147" t="s">
         <v>30</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B148" t="s">
         <v>30</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>329</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B149" t="s">
         <v>30</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>329</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B150" t="s">
         <v>30</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>329</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B151" t="s">
         <v>30</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B152" t="s">
         <v>30</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B153" t="s">
         <v>30</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B154" t="s">
         <v>30</v>
       </c>
       <c r="C154" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="E154" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B155" t="s">
         <v>30</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B156" t="s">
         <v>30</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="90" x14ac:dyDescent="0.25">
@@ -5341,7 +5335,7 @@
         <v>388</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>392</v>
@@ -5359,7 +5353,7 @@
         <v>394</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>308</v>
@@ -5380,7 +5374,7 @@
         <v>389</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>308</v>
